--- a/research/traditional_assets/database/data/botswana/botswana_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/botswana/botswana_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0338</v>
+        <v>0.0697</v>
       </c>
       <c r="E2">
-        <v>0.0191</v>
+        <v>0.0965</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>102.88</v>
+        <v>47.889</v>
       </c>
       <c r="L2">
-        <v>0.2614485387547649</v>
+        <v>0.269341957255343</v>
       </c>
       <c r="M2">
-        <v>55.76000000000001</v>
+        <v>27.09</v>
       </c>
       <c r="N2">
-        <v>0.06010563759836155</v>
+        <v>0.05918724055057897</v>
       </c>
       <c r="O2">
-        <v>0.54199066874028</v>
+        <v>0.5656831422664913</v>
       </c>
       <c r="P2">
-        <v>55.76000000000001</v>
+        <v>27.09</v>
       </c>
       <c r="Q2">
-        <v>0.06010563759836155</v>
+        <v>0.05918724055057897</v>
       </c>
       <c r="R2">
-        <v>0.54199066874028</v>
+        <v>0.5656831422664913</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1158</v>
+        <v>166</v>
       </c>
       <c r="V2">
-        <v>1.248248356149617</v>
+        <v>0.3626829801179812</v>
       </c>
       <c r="W2">
-        <v>0.2058341527368076</v>
+        <v>0.1106255254972505</v>
       </c>
       <c r="X2">
-        <v>0.05229564338900826</v>
+        <v>0.0835993376632314</v>
       </c>
       <c r="Y2">
-        <v>0.1535385093477993</v>
+        <v>0.02702618783401908</v>
       </c>
       <c r="Z2">
-        <v>-1.486083311303297</v>
+        <v>0.5381355932203391</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04789131725196002</v>
+        <v>0.07596494762092773</v>
       </c>
       <c r="AC2">
-        <v>-0.04789131725196002</v>
+        <v>-0.07596494762092773</v>
       </c>
       <c r="AD2">
-        <v>299.3</v>
+        <v>136.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>299.3</v>
+        <v>136.8</v>
       </c>
       <c r="AG2">
-        <v>-858.7</v>
+        <v>-29.19999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2439282803585982</v>
+        <v>0.2301093355761144</v>
       </c>
       <c r="AI2">
-        <v>0.3077318527657825</v>
+        <v>0.3060402684563759</v>
       </c>
       <c r="AJ2">
-        <v>-12.4449275362319</v>
+        <v>-0.06814469078179693</v>
       </c>
       <c r="AK2">
-        <v>4.631607335490829</v>
+        <v>-0.1039145907473309</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0338</v>
+        <v>0.0697</v>
       </c>
       <c r="E3">
-        <v>0.0191</v>
+        <v>0.0965</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>38.4</v>
+        <v>47.9</v>
       </c>
       <c r="L3">
-        <v>0.2917933130699088</v>
+        <v>0.3506588579795022</v>
       </c>
       <c r="M3">
-        <v>16.1</v>
+        <v>25.8</v>
       </c>
       <c r="N3">
-        <v>0.04784546805349183</v>
+        <v>0.07493465001452222</v>
       </c>
       <c r="O3">
-        <v>0.4192708333333334</v>
+        <v>0.5386221294363257</v>
       </c>
       <c r="P3">
-        <v>16.1</v>
+        <v>25.8</v>
       </c>
       <c r="Q3">
-        <v>0.04784546805349183</v>
+        <v>0.07493465001452222</v>
       </c>
       <c r="R3">
-        <v>0.4192708333333334</v>
+        <v>0.5386221294363257</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>42.8</v>
+        <v>44.3</v>
       </c>
       <c r="V3">
-        <v>0.1271916790490342</v>
+        <v>0.1286668602962533</v>
       </c>
       <c r="W3">
-        <v>0.2105263157894737</v>
+        <v>0.2213493530499076</v>
       </c>
       <c r="X3">
-        <v>0.05229564338900826</v>
+        <v>0.08130080056858502</v>
       </c>
       <c r="Y3">
-        <v>0.1582306724004654</v>
+        <v>0.1400485524813226</v>
       </c>
       <c r="Z3">
-        <v>0.5925258892390814</v>
+        <v>0.5141136620248401</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04668230265692847</v>
+        <v>0.07454782402691391</v>
       </c>
       <c r="AC3">
-        <v>-0.04668230265692847</v>
+        <v>-0.07454782402691391</v>
       </c>
       <c r="AD3">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="AG3">
-        <v>49.3</v>
+        <v>44.40000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.2148856742883808</v>
+        <v>0.2048498845265589</v>
       </c>
       <c r="AI3">
-        <v>0.2985413290113452</v>
+        <v>0.294293297942933</v>
       </c>
       <c r="AJ3">
-        <v>0.1277864178330741</v>
+        <v>0.1142269102135323</v>
       </c>
       <c r="AK3">
-        <v>0.1855476100865638</v>
+        <v>0.1726954492415403</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First National Bank of Botswana Limited (BSM:FNBB)</t>
+          <t>Access Bank Botswana Limited (BSM:ACCESS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,12 +831,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0534</v>
-      </c>
-      <c r="E4">
-        <v>0.0634</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -850,28 +844,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>62.8</v>
+        <v>-0.011</v>
       </c>
       <c r="L4">
-        <v>0.3215565796210957</v>
+        <v>-0.0002669902912621359</v>
       </c>
       <c r="M4">
-        <v>32.6</v>
+        <v>1.29</v>
       </c>
       <c r="N4">
-        <v>0.06016980435585088</v>
+        <v>0.01137566137566138</v>
       </c>
       <c r="O4">
-        <v>0.5191082802547771</v>
+        <v>-117.2727272727273</v>
       </c>
       <c r="P4">
-        <v>32.6</v>
+        <v>1.29</v>
       </c>
       <c r="Q4">
-        <v>0.06016980435585088</v>
+        <v>0.01137566137566138</v>
       </c>
       <c r="R4">
-        <v>0.5191082802547771</v>
+        <v>-117.2727272727273</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,182 +874,60 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>867.5</v>
+        <v>121.7</v>
       </c>
       <c r="V4">
-        <v>1.601144333702473</v>
+        <v>1.073192239858906</v>
       </c>
       <c r="W4">
-        <v>0.2058341527368076</v>
+        <v>-9.830205540661304e-05</v>
       </c>
       <c r="X4">
-        <v>0.05201364073858378</v>
+        <v>0.08589787475787777</v>
       </c>
       <c r="Y4">
-        <v>0.1538205119982238</v>
+        <v>-0.08599617681328439</v>
       </c>
       <c r="Z4">
-        <v>-0.4796286745745229</v>
+        <v>0.6367851622874807</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04789131725196002</v>
+        <v>0.07738207121494156</v>
       </c>
       <c r="AC4">
-        <v>-0.04789131725196002</v>
+        <v>-0.07738207121494156</v>
       </c>
       <c r="AD4">
-        <v>141.9</v>
+        <v>48.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>141.9</v>
+        <v>48.1</v>
       </c>
       <c r="AG4">
-        <v>-725.6</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.2075471698113208</v>
+        <v>0.2978328173374613</v>
       </c>
       <c r="AI4">
-        <v>0.2828947368421053</v>
+        <v>0.3303571428571429</v>
       </c>
       <c r="AJ4">
-        <v>3.947769314472251</v>
+        <v>-1.849246231155778</v>
       </c>
       <c r="AK4">
-        <v>1.983055479639246</v>
+        <v>-3.07949790794979</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Botswana</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Standard Chartered Bank Botswana Limited (BSM:STANCHART)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.0104</v>
-      </c>
-      <c r="E5">
-        <v>-0.161</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>1.68</v>
-      </c>
-      <c r="L5">
-        <v>0.02522522522522523</v>
-      </c>
-      <c r="M5">
-        <v>7.06</v>
-      </c>
-      <c r="N5">
-        <v>0.142914979757085</v>
-      </c>
-      <c r="O5">
-        <v>4.202380952380953</v>
-      </c>
-      <c r="P5">
-        <v>7.06</v>
-      </c>
-      <c r="Q5">
-        <v>0.142914979757085</v>
-      </c>
-      <c r="R5">
-        <v>4.202380952380953</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>247.7</v>
-      </c>
-      <c r="V5">
-        <v>5.01417004048583</v>
-      </c>
-      <c r="W5">
-        <v>0.01755485893416928</v>
-      </c>
-      <c r="X5">
-        <v>0.0773556144890656</v>
-      </c>
-      <c r="Y5">
-        <v>-0.05980075555489632</v>
-      </c>
-      <c r="Z5">
-        <v>-0.8356336260978671</v>
-      </c>
-      <c r="AA5">
-        <v>-0</v>
-      </c>
-      <c r="AB5">
-        <v>0.04821688533030754</v>
-      </c>
-      <c r="AC5">
-        <v>-0.04821688533030754</v>
-      </c>
-      <c r="AD5">
-        <v>65.3</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>65.3</v>
-      </c>
-      <c r="AG5">
-        <v>-182.4</v>
-      </c>
-      <c r="AH5">
-        <v>0.5693112467306016</v>
-      </c>
-      <c r="AI5">
-        <v>0.4018461538461539</v>
-      </c>
-      <c r="AJ5">
-        <v>1.371428571428571</v>
-      </c>
-      <c r="AK5">
-        <v>2.140845070422535</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/botswana/botswana_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/botswana/botswana_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0697</v>
+        <v>0.077</v>
       </c>
       <c r="E2">
-        <v>0.0965</v>
+        <v>0.103</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>47.889</v>
+        <v>53.4</v>
       </c>
       <c r="L2">
-        <v>0.269341957255343</v>
+        <v>0.3675154852030282</v>
       </c>
       <c r="M2">
-        <v>27.09</v>
+        <v>33</v>
       </c>
       <c r="N2">
-        <v>0.05918724055057897</v>
+        <v>0.08196721311475409</v>
       </c>
       <c r="O2">
-        <v>0.5656831422664913</v>
+        <v>0.6179775280898877</v>
       </c>
       <c r="P2">
-        <v>27.09</v>
+        <v>33</v>
       </c>
       <c r="Q2">
-        <v>0.05918724055057897</v>
+        <v>0.08196721311475409</v>
       </c>
       <c r="R2">
-        <v>0.5656831422664913</v>
+        <v>0.6179775280898877</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>166</v>
+        <v>37.4</v>
       </c>
       <c r="V2">
-        <v>0.3626829801179812</v>
+        <v>0.09289617486338797</v>
       </c>
       <c r="W2">
-        <v>0.1106255254972505</v>
+        <v>0.2510578279266573</v>
       </c>
       <c r="X2">
-        <v>0.0835993376632314</v>
+        <v>0.06893049219905058</v>
       </c>
       <c r="Y2">
-        <v>0.02702618783401908</v>
+        <v>0.1821273357276067</v>
       </c>
       <c r="Z2">
-        <v>0.5381355932203391</v>
+        <v>0.5651497471800857</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07596494762092773</v>
+        <v>0.06402089709134014</v>
       </c>
       <c r="AC2">
-        <v>-0.07596494762092773</v>
+        <v>-0.06402089709134014</v>
       </c>
       <c r="AD2">
-        <v>136.8</v>
+        <v>105.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>136.8</v>
+        <v>105.7</v>
       </c>
       <c r="AG2">
-        <v>-29.19999999999999</v>
+        <v>68.30000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.2301093355761144</v>
+        <v>0.207948062168011</v>
       </c>
       <c r="AI2">
-        <v>0.3060402684563759</v>
+        <v>0.3286691542288557</v>
       </c>
       <c r="AJ2">
-        <v>-0.06814469078179693</v>
+        <v>0.1450414100658314</v>
       </c>
       <c r="AK2">
-        <v>-0.1039145907473309</v>
+        <v>0.2403237156931738</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0697</v>
+        <v>0.077</v>
       </c>
       <c r="E3">
-        <v>0.0965</v>
+        <v>0.103</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>47.9</v>
+        <v>53.4</v>
       </c>
       <c r="L3">
-        <v>0.3506588579795022</v>
+        <v>0.3675154852030282</v>
       </c>
       <c r="M3">
-        <v>25.8</v>
+        <v>33</v>
       </c>
       <c r="N3">
-        <v>0.07493465001452222</v>
+        <v>0.08196721311475409</v>
       </c>
       <c r="O3">
-        <v>0.5386221294363257</v>
+        <v>0.6179775280898877</v>
       </c>
       <c r="P3">
-        <v>25.8</v>
+        <v>33</v>
       </c>
       <c r="Q3">
-        <v>0.07493465001452222</v>
+        <v>0.08196721311475409</v>
       </c>
       <c r="R3">
-        <v>0.5386221294363257</v>
+        <v>0.6179775280898877</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,176 +758,60 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>44.3</v>
+        <v>37.4</v>
       </c>
       <c r="V3">
-        <v>0.1286668602962533</v>
+        <v>0.09289617486338797</v>
       </c>
       <c r="W3">
-        <v>0.2213493530499076</v>
+        <v>0.2510578279266573</v>
       </c>
       <c r="X3">
-        <v>0.08130080056858502</v>
+        <v>0.06893049219905058</v>
       </c>
       <c r="Y3">
-        <v>0.1400485524813226</v>
+        <v>0.1821273357276067</v>
       </c>
       <c r="Z3">
-        <v>0.5141136620248401</v>
+        <v>0.5651497471800857</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07454782402691391</v>
+        <v>0.06402089709134014</v>
       </c>
       <c r="AC3">
-        <v>-0.07454782402691391</v>
+        <v>-0.06402089709134014</v>
       </c>
       <c r="AD3">
-        <v>88.7</v>
+        <v>105.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>88.7</v>
+        <v>105.7</v>
       </c>
       <c r="AG3">
-        <v>44.40000000000001</v>
+        <v>68.30000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.2048498845265589</v>
+        <v>0.207948062168011</v>
       </c>
       <c r="AI3">
-        <v>0.294293297942933</v>
+        <v>0.3286691542288557</v>
       </c>
       <c r="AJ3">
-        <v>0.1142269102135323</v>
+        <v>0.1450414100658314</v>
       </c>
       <c r="AK3">
-        <v>0.1726954492415403</v>
+        <v>0.2403237156931738</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Botswana</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Access Bank Botswana Limited (BSM:ACCESS)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>-0.011</v>
-      </c>
-      <c r="L4">
-        <v>-0.0002669902912621359</v>
-      </c>
-      <c r="M4">
-        <v>1.29</v>
-      </c>
-      <c r="N4">
-        <v>0.01137566137566138</v>
-      </c>
-      <c r="O4">
-        <v>-117.2727272727273</v>
-      </c>
-      <c r="P4">
-        <v>1.29</v>
-      </c>
-      <c r="Q4">
-        <v>0.01137566137566138</v>
-      </c>
-      <c r="R4">
-        <v>-117.2727272727273</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>121.7</v>
-      </c>
-      <c r="V4">
-        <v>1.073192239858906</v>
-      </c>
-      <c r="W4">
-        <v>-9.830205540661304e-05</v>
-      </c>
-      <c r="X4">
-        <v>0.08589787475787777</v>
-      </c>
-      <c r="Y4">
-        <v>-0.08599617681328439</v>
-      </c>
-      <c r="Z4">
-        <v>0.6367851622874807</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07738207121494156</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07738207121494156</v>
-      </c>
-      <c r="AD4">
-        <v>48.1</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>48.1</v>
-      </c>
-      <c r="AG4">
-        <v>-73.59999999999999</v>
-      </c>
-      <c r="AH4">
-        <v>0.2978328173374613</v>
-      </c>
-      <c r="AI4">
-        <v>0.3303571428571429</v>
-      </c>
-      <c r="AJ4">
-        <v>-1.849246231155778</v>
-      </c>
-      <c r="AK4">
-        <v>-3.07949790794979</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>
